--- a/tame_output/ON/bt/strategyON_20240824.xlsx
+++ b/tame_output/ON/bt/strategyON_20240824.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.1%</t>
+          <t>-662.0%</t>
         </is>
       </c>
     </row>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.73857063885366</v>
+        <v>3.738570638853659</v>
       </c>
       <c r="C2065" t="n">
         <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.004821579907257</v>
+        <v>-5.004528003683902</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.208083844454476</v>
+        <v>2.208201274943818</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6828838629545593</v>

--- a/tame_output/ON/bt/strategyON_20240824.xlsx
+++ b/tame_output/ON/bt/strategyON_20240824.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.0%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.0%</t>
+          <t>-668.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-158.1%</t>
         </is>
       </c>
     </row>
@@ -49046,10 +49046,10 @@
         <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.004528003683902</v>
+        <v>-5.073046309808004</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.208201274943818</v>
+        <v>2.180793952494177</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6828838629545593</v>

--- a/tame_output/ON/bt/strategyON_20240824.xlsx
+++ b/tame_output/ON/bt/strategyON_20240824.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>105.2%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>-29.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2065"/>
+  <dimension ref="A1:G2066"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.738570638853659</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.210368900731126</v>
@@ -49056,6 +49056,29 @@
       </c>
       <c r="G2065" t="n">
         <v>4.620099218503862</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="2" t="n">
+        <v>45528</v>
+      </c>
+      <c r="B2066" t="n">
+        <v>3.74119489745307</v>
+      </c>
+      <c r="C2066" t="n">
+        <v>4.16860273758294</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>-5.073046309808004</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>2.180793952494177</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>0.6828838629545593</v>
+      </c>
+      <c r="G2066" t="n">
+        <v>4.161666534569308</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240824.xlsx
+++ b/tame_output/ON/bt/strategyON_20240824.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>105.2%</t>
+          <t>99.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.9%</t>
+          <t>430.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.9%</t>
+          <t>-676.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.1%</t>
+          <t>-161.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.3%</t>
+          <t>-331.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-170.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-35.5%</t>
         </is>
       </c>
     </row>
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.265990269968155</v>
+        <v>-4.413126597052681</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.139225562225141</v>
+        <v>2.08037103139133</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.8421524048739697</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.439551333701248</v>
+        <v>4.351269537450532</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.289432309148242</v>
+        <v>-4.436568636232768</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.150051416726701</v>
+        <v>2.09119688589289</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.8421524048739697</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.459754003874842</v>
+        <v>4.371472207624127</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.307504817439853</v>
+        <v>-4.45464114452438</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.142822413410056</v>
+        <v>2.083967882576245</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.8421524048739697</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.459754003874842</v>
+        <v>4.371472207624127</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.538678611316485</v>
+        <v>-4.685814938401012</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.010604809452869</v>
+        <v>1.951750278619059</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.8421524048739697</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.420005917468308</v>
+        <v>4.331724121217593</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.50739259077603</v>
+        <v>-4.654528917860556</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.030141836665992</v>
+        <v>1.971287305832181</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.020574752498951</v>
+        <v>0.8734384254144251</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.445800148789522</v>
+        <v>4.357518352538806</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.354367198662746</v>
+        <v>-4.501503525747272</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.190522993084209</v>
+        <v>2.131668462250399</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.173600144612235</v>
+        <v>1.026463817527709</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.636786383630397</v>
+        <v>4.54850458737968</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.382674512536016</v>
+        <v>-4.529810839620542</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.366666292443194</v>
+        <v>2.307811761609384</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.173600144612235</v>
+        <v>1.026463817527709</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.824252608538689</v>
+        <v>4.735970812287974</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.549267737649538</v>
+        <v>-4.696404064734065</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.269431953751867</v>
+        <v>2.210577422918057</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.007006919498713</v>
+        <v>0.8598705924141867</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.693699624824657</v>
+        <v>4.605417828573942</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.376203358267238</v>
+        <v>-4.523339685351765</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.342334108166505</v>
+        <v>2.283479577332694</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.007006919498713</v>
+        <v>0.8598705924141867</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.697376027486375</v>
+        <v>4.60909423123566</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.346957377811542</v>
+        <v>-4.494093704896068</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.351650555472279</v>
+        <v>2.292796024638468</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.007006919498713</v>
+        <v>0.8598705924141867</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.69499408260987</v>
+        <v>4.606712286359155</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.453882925689393</v>
+        <v>-4.601019252773919</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.306173575478773</v>
+        <v>2.247319044644963</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9000813716208612</v>
+        <v>0.7529450445363354</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.628131993040795</v>
+        <v>4.539850196790079</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.598901484196642</v>
+        <v>-4.746037811281168</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.249594954219108</v>
+        <v>2.190740423385297</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7550628131136127</v>
+        <v>0.6079264860290868</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.54254966007968</v>
+        <v>4.454267863828965</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.717243249981359</v>
+        <v>-4.864379577065885</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.302189487162974</v>
+        <v>2.243334956329163</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.6186125245919769</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.648892522475167</v>
+        <v>4.560610726224452</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.768653672302067</v>
+        <v>-4.915789999386593</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.27941101536063</v>
+        <v>2.220556484526819</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.6186125245919769</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.646678219601106</v>
+        <v>4.55839642335039</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.848073123509819</v>
+        <v>-4.995209450594345</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.247546362951819</v>
+        <v>2.188691832118008</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.6186125245919769</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.646581347675395</v>
+        <v>4.55829955142468</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.943536121427036</v>
+        <v>-5.090672448511563</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.209355057342975</v>
+        <v>2.150500526509164</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.6186125245919769</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.646575241233439</v>
+        <v>4.558293444982723</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.98355611947082</v>
+        <v>-5.130692446555346</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.191443454688072</v>
+        <v>2.132588923854262</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7257288536327189</v>
+        <v>0.578592526548193</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.620659638969779</v>
+        <v>4.532377842719064</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.038925281603014</v>
+        <v>-5.18606160868754</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.175029607582921</v>
+        <v>2.116175076749111</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7257288536327189</v>
+        <v>0.578592526548193</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.626393456717506</v>
+        <v>4.53811166046679</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.084363061433841</v>
+        <v>-5.231499388518367</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.156392858993523</v>
+        <v>2.097538328159713</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6828838629545593</v>
+        <v>0.5357475358700334</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.600224825653543</v>
+        <v>4.511943029402827</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.073046309808004</v>
+        <v>-5.148273931670703</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.180793952494177</v>
+        <v>2.150702903749098</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6828838629545593</v>
+        <v>0.5357475358700334</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.620099218503862</v>
+        <v>4.531817422253146</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.74119489745307</v>
+        <v>3.701450098606097</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.16860273758294</v>
+        <v>4.112238436600323</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.073046309808004</v>
+        <v>-5.148273931670703</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.180793952494177</v>
+        <v>2.150702903749098</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6828838629545593</v>
+        <v>0.5357475358700334</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.161666534569308</v>
+        <v>4.10530223358669</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240824.xlsx
+++ b/tame_output/ON/bt/strategyON_20240824.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>107.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.2%</t>
+          <t>430.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.4%</t>
+          <t>-665.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-158.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -49066,19 +49066,19 @@
         <v>3.701450098606097</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.112238436600323</v>
+        <v>4.194069601255854</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.148273931670703</v>
+        <v>-5.034064986219011</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.150702903749098</v>
+        <v>2.180087182454502</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5357475358700334</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.10530223358669</v>
+        <v>4.515518122777874</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240824.xlsx
+++ b/tame_output/ON/bt/strategyON_20240824.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-46.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.5%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.0%</t>
+          <t>-665.1%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.2%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -49069,10 +49069,10 @@
         <v>4.194069601255854</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.034064986219011</v>
+        <v>-5.035154716514165</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.180087182454502</v>
+        <v>2.17965129033644</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5357475358700334</v>
